--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD326"/>
+  <dimension ref="A1:AD329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31662,10 +31662,10 @@
         <v>360.63</v>
       </c>
       <c r="P326" t="n">
-        <v>339.41</v>
+        <v>355.8</v>
       </c>
       <c r="Q326" t="n">
-        <v>371.21</v>
+        <v>366.58</v>
       </c>
       <c r="R326" t="n">
         <v>371.93</v>
@@ -31704,6 +31704,294 @@
         <v>315.11</v>
       </c>
       <c r="AD326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>357.92</v>
+      </c>
+      <c r="C327" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="D327" t="n">
+        <v>334.24</v>
+      </c>
+      <c r="E327" t="n">
+        <v>332.3</v>
+      </c>
+      <c r="F327" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="G327" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="H327" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="I327" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="J327" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="K327" t="n">
+        <v>346.46</v>
+      </c>
+      <c r="L327" t="n">
+        <v>361.21</v>
+      </c>
+      <c r="M327" t="n">
+        <v>366.53</v>
+      </c>
+      <c r="N327" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="O327" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="P327" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="R327" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="S327" t="n">
+        <v>373</v>
+      </c>
+      <c r="T327" t="n">
+        <v>371.84</v>
+      </c>
+      <c r="U327" t="n">
+        <v>367.53</v>
+      </c>
+      <c r="V327" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="W327" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="X327" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>360.53</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>354.51</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="C328" t="n">
+        <v>343.71</v>
+      </c>
+      <c r="D328" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="E328" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="F328" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="G328" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="H328" t="n">
+        <v>325.27</v>
+      </c>
+      <c r="I328" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="J328" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="K328" t="n">
+        <v>349.01</v>
+      </c>
+      <c r="L328" t="n">
+        <v>362.63</v>
+      </c>
+      <c r="M328" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="N328" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="O328" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="P328" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>371.31</v>
+      </c>
+      <c r="R328" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="S328" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="T328" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="U328" t="n">
+        <v>369.42</v>
+      </c>
+      <c r="V328" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="W328" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="X328" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>284.37</v>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>357.87</v>
+      </c>
+      <c r="C329" t="n">
+        <v>342.98</v>
+      </c>
+      <c r="D329" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="E329" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="F329" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="G329" t="n">
+        <v>328.62</v>
+      </c>
+      <c r="H329" t="n">
+        <v>325.54</v>
+      </c>
+      <c r="I329" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="J329" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="K329" t="n">
+        <v>350.93</v>
+      </c>
+      <c r="L329" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="M329" t="n">
+        <v>364.67</v>
+      </c>
+      <c r="N329" t="n">
+        <v>370</v>
+      </c>
+      <c r="O329" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="P329" t="n">
+        <v>361.22</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="R329" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="S329" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="T329" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="U329" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="V329" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="W329" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="X329" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>361.41</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>353.58</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>284.37</v>
+      </c>
+      <c r="AD329" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31720,7 +32008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35023,6 +35311,36 @@
       </c>
       <c r="B330" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -35191,28 +35509,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6454104553429684</v>
+        <v>-0.6307458219607904</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3731879496339792</v>
+        <v>0.3626679963268912</v>
       </c>
       <c r="M2" t="n">
-        <v>4.966117339452373</v>
+        <v>5.010239047143869</v>
       </c>
       <c r="N2" t="n">
-        <v>37.37207922382376</v>
+        <v>37.67362015486183</v>
       </c>
       <c r="O2" t="n">
-        <v>6.113270746811707</v>
+        <v>6.137884012822483</v>
       </c>
       <c r="P2" t="n">
-        <v>367.0141773569816</v>
+        <v>366.8515576735019</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35269,28 +35587,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5343896571475019</v>
+        <v>-0.5235960263100882</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3314253846478868</v>
+        <v>0.3238672630585502</v>
       </c>
       <c r="M3" t="n">
-        <v>4.435120059587786</v>
+        <v>4.453064488584364</v>
       </c>
       <c r="N3" t="n">
-        <v>30.77129293554096</v>
+        <v>30.84108812838864</v>
       </c>
       <c r="O3" t="n">
-        <v>5.547187840297187</v>
+        <v>5.553475319868509</v>
       </c>
       <c r="P3" t="n">
-        <v>350.8402228202811</v>
+        <v>350.7205226777692</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35347,28 +35665,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3420581880274826</v>
+        <v>-0.3356709853388611</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2816570130517622</v>
+        <v>0.2761421942968122</v>
       </c>
       <c r="M4" t="n">
-        <v>3.119213826062209</v>
+        <v>3.130578544159193</v>
       </c>
       <c r="N4" t="n">
-        <v>15.9395776967436</v>
+        <v>15.91549654990531</v>
       </c>
       <c r="O4" t="n">
-        <v>3.99244006802151</v>
+        <v>3.989423084846393</v>
       </c>
       <c r="P4" t="n">
-        <v>339.4579025446595</v>
+        <v>339.387076085483</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35425,28 +35743,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07492933368374681</v>
+        <v>-0.06257532051532178</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01466571751018653</v>
+        <v>0.01022668694711726</v>
       </c>
       <c r="M5" t="n">
-        <v>3.315778650366274</v>
+        <v>3.35622459046748</v>
       </c>
       <c r="N5" t="n">
-        <v>20.14881742881064</v>
+        <v>20.42109563397955</v>
       </c>
       <c r="O5" t="n">
-        <v>4.488743413118046</v>
+        <v>4.518970638760507</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5578535410596</v>
+        <v>326.4208650468717</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35503,28 +35821,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1163021191175902</v>
+        <v>-0.0973550663921483</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02014285100053803</v>
+        <v>0.01402913943958339</v>
       </c>
       <c r="M6" t="n">
-        <v>4.773825492606385</v>
+        <v>4.823703304348346</v>
       </c>
       <c r="N6" t="n">
-        <v>35.14654376294001</v>
+        <v>35.8940330412868</v>
       </c>
       <c r="O6" t="n">
-        <v>5.928452054536666</v>
+        <v>5.991162912263929</v>
       </c>
       <c r="P6" t="n">
-        <v>321.613076051488</v>
+        <v>321.402972691408</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35581,28 +35899,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3633532089080941</v>
+        <v>-0.3394137018413315</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1051344627911613</v>
+        <v>0.0921103294795802</v>
       </c>
       <c r="M7" t="n">
-        <v>6.395317978960123</v>
+        <v>6.463884219446611</v>
       </c>
       <c r="N7" t="n">
-        <v>60.02556070004513</v>
+        <v>61.18649496442377</v>
       </c>
       <c r="O7" t="n">
-        <v>7.74761645282245</v>
+        <v>7.822179681164565</v>
       </c>
       <c r="P7" t="n">
-        <v>324.0501886378518</v>
+        <v>323.7847077469918</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35659,28 +35977,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4790436235990172</v>
+        <v>-0.4636610152670244</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1394081212779413</v>
+        <v>0.1327473899444275</v>
       </c>
       <c r="M8" t="n">
-        <v>6.964822811545561</v>
+        <v>6.982526296979177</v>
       </c>
       <c r="N8" t="n">
-        <v>75.67019253008405</v>
+        <v>75.68204942083646</v>
       </c>
       <c r="O8" t="n">
-        <v>8.698861565175299</v>
+        <v>8.699543058163254</v>
       </c>
       <c r="P8" t="n">
-        <v>329.2313142476148</v>
+        <v>329.060731422783</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35737,28 +36055,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5009874611804721</v>
+        <v>-0.4673214402943882</v>
       </c>
       <c r="J9" t="n">
+        <v>328</v>
+      </c>
+      <c r="K9" t="n">
         <v>325</v>
       </c>
-      <c r="K9" t="n">
-        <v>322</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1255724641972914</v>
+        <v>0.1093067047728236</v>
       </c>
       <c r="M9" t="n">
-        <v>7.586929642177376</v>
+        <v>7.692992135312491</v>
       </c>
       <c r="N9" t="n">
-        <v>93.27520778107781</v>
+        <v>95.79439224035974</v>
       </c>
       <c r="O9" t="n">
-        <v>9.657909079147402</v>
+        <v>9.7874609700555</v>
       </c>
       <c r="P9" t="n">
-        <v>336.1030655047521</v>
+        <v>335.7284407551868</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35815,28 +36133,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5045532888687313</v>
+        <v>-0.4752548226377855</v>
       </c>
       <c r="J10" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K10" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1386160116848412</v>
+        <v>0.1236115213423041</v>
       </c>
       <c r="M10" t="n">
-        <v>7.390887340356855</v>
+        <v>7.486075041796251</v>
       </c>
       <c r="N10" t="n">
-        <v>84.26927461683185</v>
+        <v>86.04614024204901</v>
       </c>
       <c r="O10" t="n">
-        <v>9.179829770580271</v>
+        <v>9.276105877039621</v>
       </c>
       <c r="P10" t="n">
-        <v>347.6248218917082</v>
+        <v>347.29871447059</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35893,28 +36211,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4321158699646812</v>
+        <v>-0.4212469035986709</v>
       </c>
       <c r="J11" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K11" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07823122062050303</v>
+        <v>0.07565889736167242</v>
       </c>
       <c r="M11" t="n">
-        <v>8.703879017198668</v>
+        <v>8.678484770137009</v>
       </c>
       <c r="N11" t="n">
-        <v>116.619405286314</v>
+        <v>115.9279701673294</v>
       </c>
       <c r="O11" t="n">
-        <v>10.79904649894212</v>
+        <v>10.76698519397744</v>
       </c>
       <c r="P11" t="n">
-        <v>354.0451796544032</v>
+        <v>353.9239623586253</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35971,28 +36289,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3879968752181795</v>
+        <v>-0.3651528759692116</v>
       </c>
       <c r="J12" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K12" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05960467191299679</v>
+        <v>0.05343911536635992</v>
       </c>
       <c r="M12" t="n">
-        <v>8.937111127445803</v>
+        <v>8.985023237077504</v>
       </c>
       <c r="N12" t="n">
-        <v>126.8680192757839</v>
+        <v>127.2655445886541</v>
       </c>
       <c r="O12" t="n">
-        <v>11.26357044971903</v>
+        <v>11.28120315341649</v>
       </c>
       <c r="P12" t="n">
-        <v>359.4114846862557</v>
+        <v>359.1581493960603</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36049,28 +36367,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5315451132814291</v>
+        <v>-0.5079889435433974</v>
       </c>
       <c r="J13" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K13" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09029088756243808</v>
+        <v>0.08365482082288156</v>
       </c>
       <c r="M13" t="n">
-        <v>9.712437417912588</v>
+        <v>9.74403439902636</v>
       </c>
       <c r="N13" t="n">
-        <v>150.8924061367284</v>
+        <v>151.153837252889</v>
       </c>
       <c r="O13" t="n">
-        <v>12.28382701509299</v>
+        <v>12.29446368301151</v>
       </c>
       <c r="P13" t="n">
-        <v>365.5999056362745</v>
+        <v>365.3372692848679</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36127,28 +36445,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4806639318491535</v>
+        <v>-0.4558953923462876</v>
       </c>
       <c r="J14" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K14" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07098539135646287</v>
+        <v>0.064710620784177</v>
       </c>
       <c r="M14" t="n">
-        <v>9.82676338475258</v>
+        <v>9.860655852251144</v>
       </c>
       <c r="N14" t="n">
-        <v>160.2747591562502</v>
+        <v>160.6361820116757</v>
       </c>
       <c r="O14" t="n">
-        <v>12.65996679127754</v>
+        <v>12.67423299500509</v>
       </c>
       <c r="P14" t="n">
-        <v>369.5088409809098</v>
+        <v>369.2326963583583</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36205,28 +36523,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9319702263533987</v>
+        <v>-0.9191756723424944</v>
       </c>
       <c r="J15" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K15" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2266583064083286</v>
+        <v>0.2244289792102171</v>
       </c>
       <c r="M15" t="n">
-        <v>9.535695089877024</v>
+        <v>9.499839632759533</v>
       </c>
       <c r="N15" t="n">
-        <v>157.0841489487881</v>
+        <v>156.1285092609833</v>
       </c>
       <c r="O15" t="n">
-        <v>12.53332154493724</v>
+        <v>12.49513942543193</v>
       </c>
       <c r="P15" t="n">
-        <v>380.8660710935862</v>
+        <v>380.7234223841172</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36283,28 +36601,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6452030810413942</v>
+        <v>-0.6340578597479674</v>
       </c>
       <c r="J16" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K16" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L16" t="n">
-        <v>0.13651087566375</v>
+        <v>0.1354282671838974</v>
       </c>
       <c r="M16" t="n">
-        <v>9.013243664064484</v>
+        <v>8.903203625349759</v>
       </c>
       <c r="N16" t="n">
-        <v>137.5319149446225</v>
+        <v>135.2470489155959</v>
       </c>
       <c r="O16" t="n">
-        <v>11.7274001784122</v>
+        <v>11.62957647189251</v>
       </c>
       <c r="P16" t="n">
-        <v>375.3107080073046</v>
+        <v>375.1858010026948</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36361,28 +36679,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.826397332230092</v>
+        <v>-0.8002131296937743</v>
       </c>
       <c r="J17" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K17" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1281791892507206</v>
+        <v>0.1221935801946132</v>
       </c>
       <c r="M17" t="n">
-        <v>12.09731298973556</v>
+        <v>12.09082413368565</v>
       </c>
       <c r="N17" t="n">
-        <v>244.6941759704908</v>
+        <v>244.4865969485718</v>
       </c>
       <c r="O17" t="n">
-        <v>15.64270360169529</v>
+        <v>15.6360671829131</v>
       </c>
       <c r="P17" t="n">
-        <v>377.7259660471799</v>
+        <v>377.4326867617013</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36439,28 +36757,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4162904739393103</v>
+        <v>-0.3939675720757848</v>
       </c>
       <c r="J18" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K18" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05237044409456793</v>
+        <v>0.04757114500754345</v>
       </c>
       <c r="M18" t="n">
-        <v>10.15691555389764</v>
+        <v>10.16297515362089</v>
       </c>
       <c r="N18" t="n">
-        <v>166.5259608346351</v>
+        <v>166.4761012641894</v>
       </c>
       <c r="O18" t="n">
-        <v>12.90449382326308</v>
+        <v>12.90256181012862</v>
       </c>
       <c r="P18" t="n">
-        <v>375.9183320207111</v>
+        <v>375.6696969931199</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36517,28 +36835,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2176644511614652</v>
+        <v>-0.1998530557861724</v>
       </c>
       <c r="J19" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K19" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01471034528772464</v>
+        <v>0.01258346396438947</v>
       </c>
       <c r="M19" t="n">
-        <v>10.64206694167347</v>
+        <v>10.63360774482824</v>
       </c>
       <c r="N19" t="n">
-        <v>167.8515418764325</v>
+        <v>167.2459236554337</v>
       </c>
       <c r="O19" t="n">
-        <v>12.95575323462255</v>
+        <v>12.9323595548312</v>
       </c>
       <c r="P19" t="n">
-        <v>369.1331765912909</v>
+        <v>368.9343426338896</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36595,28 +36913,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.007269657007791379</v>
+        <v>0.01427220193580357</v>
       </c>
       <c r="J20" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K20" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L20" t="n">
-        <v>1.433941661466154e-05</v>
+        <v>5.58713272001965e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.16849696246229</v>
+        <v>11.17421427946538</v>
       </c>
       <c r="N20" t="n">
-        <v>196.8591808284304</v>
+        <v>196.4449215487563</v>
       </c>
       <c r="O20" t="n">
-        <v>14.03065147555274</v>
+        <v>14.0158810478955</v>
       </c>
       <c r="P20" t="n">
-        <v>360.6941104901584</v>
+        <v>360.455218264668</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36673,28 +36991,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05306395603712119</v>
+        <v>0.06841443613666409</v>
       </c>
       <c r="J21" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K21" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0008904920804242433</v>
+        <v>0.00149979816626189</v>
       </c>
       <c r="M21" t="n">
-        <v>10.15639868273884</v>
+        <v>10.12443599172041</v>
       </c>
       <c r="N21" t="n">
-        <v>166.9212008748657</v>
+        <v>166.0742840962383</v>
       </c>
       <c r="O21" t="n">
-        <v>12.91979879390023</v>
+        <v>12.8869811863073</v>
       </c>
       <c r="P21" t="n">
-        <v>358.4670164337988</v>
+        <v>358.2950427354998</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36751,28 +37069,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1979191131058211</v>
+        <v>0.2119965223567154</v>
       </c>
       <c r="J22" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K22" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01126046897101518</v>
+        <v>0.0130861870707587</v>
       </c>
       <c r="M22" t="n">
-        <v>10.73641937829053</v>
+        <v>10.69452385070532</v>
       </c>
       <c r="N22" t="n">
-        <v>181.7314590249114</v>
+        <v>180.6404984441727</v>
       </c>
       <c r="O22" t="n">
-        <v>13.48078109847168</v>
+        <v>13.44025663609787</v>
       </c>
       <c r="P22" t="n">
-        <v>353.3005089389295</v>
+        <v>353.1427930817131</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36829,28 +37147,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1492724605410223</v>
+        <v>0.1879997594029888</v>
       </c>
       <c r="J23" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K23" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005761470292498072</v>
+        <v>0.009073791443297785</v>
       </c>
       <c r="M23" t="n">
-        <v>11.55995934769383</v>
+        <v>11.650035805482</v>
       </c>
       <c r="N23" t="n">
-        <v>203.3882747480476</v>
+        <v>205.9685340251564</v>
       </c>
       <c r="O23" t="n">
-        <v>14.26142611200043</v>
+        <v>14.35160388336985</v>
       </c>
       <c r="P23" t="n">
-        <v>347.2874063142157</v>
+        <v>346.8550736701577</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36907,28 +37225,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1163410887465244</v>
+        <v>0.1573257218285524</v>
       </c>
       <c r="J24" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K24" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004462159305647195</v>
+        <v>0.008026102914195143</v>
       </c>
       <c r="M24" t="n">
-        <v>9.836714571697769</v>
+        <v>9.960506252816435</v>
       </c>
       <c r="N24" t="n">
-        <v>159.7306339665092</v>
+        <v>163.2408152683304</v>
       </c>
       <c r="O24" t="n">
-        <v>12.63845852810022</v>
+        <v>12.77657290780006</v>
       </c>
       <c r="P24" t="n">
-        <v>346.4509105358456</v>
+        <v>345.9933831961844</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36985,28 +37303,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04038967223821376</v>
+        <v>0.07232859480265688</v>
       </c>
       <c r="J25" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K25" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0004998107953700925</v>
+        <v>0.001602074107611817</v>
       </c>
       <c r="M25" t="n">
-        <v>10.47760240347335</v>
+        <v>10.56403901251327</v>
       </c>
       <c r="N25" t="n">
-        <v>172.5548510055466</v>
+        <v>173.9702121346163</v>
       </c>
       <c r="O25" t="n">
-        <v>13.13601351268895</v>
+        <v>13.18977680382107</v>
       </c>
       <c r="P25" t="n">
-        <v>342.0723783781711</v>
+        <v>341.7158458670073</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37063,28 +37381,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.24576026540917</v>
+        <v>0.2606830927493058</v>
       </c>
       <c r="J26" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K26" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01512371691209302</v>
+        <v>0.01723214273574414</v>
       </c>
       <c r="M26" t="n">
-        <v>11.56331283147489</v>
+        <v>11.53161942507553</v>
       </c>
       <c r="N26" t="n">
-        <v>210.0932101315498</v>
+        <v>208.8379809482023</v>
       </c>
       <c r="O26" t="n">
-        <v>14.49459244447907</v>
+        <v>14.45122766231998</v>
       </c>
       <c r="P26" t="n">
-        <v>338.5218031286424</v>
+        <v>338.3563263254336</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37141,28 +37459,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09242389903370048</v>
+        <v>-0.08501567873472152</v>
       </c>
       <c r="J27" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K27" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001563239464677513</v>
+        <v>0.00134491346146226</v>
       </c>
       <c r="M27" t="n">
-        <v>11.94505498992777</v>
+        <v>11.89056426536364</v>
       </c>
       <c r="N27" t="n">
-        <v>291.4265844550728</v>
+        <v>289.1953637259375</v>
       </c>
       <c r="O27" t="n">
-        <v>17.07122094213161</v>
+        <v>17.00574502119614</v>
       </c>
       <c r="P27" t="n">
-        <v>339.2916105464372</v>
+        <v>339.2095401138375</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -37219,28 +37537,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1976775045286513</v>
+        <v>-0.1870230754629651</v>
       </c>
       <c r="J28" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K28" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01519119894497922</v>
+        <v>0.013827581442031</v>
       </c>
       <c r="M28" t="n">
-        <v>9.294652381953936</v>
+        <v>9.265016762570019</v>
       </c>
       <c r="N28" t="n">
-        <v>135.3131213099225</v>
+        <v>134.4216157084351</v>
       </c>
       <c r="O28" t="n">
-        <v>11.63241683013132</v>
+        <v>11.59403362546595</v>
       </c>
       <c r="P28" t="n">
-        <v>348.4067768948879</v>
+        <v>348.28864046671</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -37297,28 +37615,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1188559820840525</v>
+        <v>0.01213778886745289</v>
       </c>
       <c r="J29" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K29" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002523703264684096</v>
+        <v>2.419347622495405e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>10.34938084918266</v>
+        <v>10.87971967539132</v>
       </c>
       <c r="N29" t="n">
-        <v>293.8653107086049</v>
+        <v>323.4717552683244</v>
       </c>
       <c r="O29" t="n">
-        <v>17.14250013004535</v>
+        <v>17.9853205495016</v>
       </c>
       <c r="P29" t="n">
-        <v>344.7268827811891</v>
+        <v>345.9187263018569</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -37356,7 +37674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD326"/>
+  <dimension ref="A1:AD329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86689,12 +87007,12 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>-38.37549604545196,174.65997781006897</t>
+          <t>-38.3754553406348,174.65979748511975</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>-38.37473980462742,174.65988687958978</t>
+          <t>-38.374752160923656,174.65993749386928</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -86758,6 +87076,462 @@
         </is>
       </c>
       <c r="AD326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-38.384547747433025,174.65503566552354</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-38.3839753575935,174.65559308415635</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-38.38337138621508,174.65606513453835</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-38.382745260497686,174.65647730369628</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-38.382121045086215,174.65689465244822</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-38.38149782029917,174.6573146943474</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-38.38087106455198,174.65772520495779</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-38.38017513879537,174.65794872534238</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-38.379505414237535,174.65825137762042</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-38.378853831497125,174.65860813929729</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-38.37814000579556,174.6587053824793</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-38.3774522773512,174.65890499492153</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-38.37676094156179,174.6590886550758</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-38.37610869078648,174.65944549141537</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-38.3754553406348,174.65979748511975</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-38.3747358015029,174.65987048187858</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-38.37404780369608,174.6601026259401</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>-38.37340553211469,174.66048871475624</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>-38.37275231647152,174.66082514496196</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>-38.372109019266645,174.661195352661</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>-38.37145992353511,174.6615441331593</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>-38.37078479371186,174.6618022276636</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>-38.370125815942934,174.66211939557357</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>-38.36949429623669,174.6625339634691</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>-38.36885250154134,174.66291211272397</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>-38.36821718834259,174.66331871363332</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>-38.36753548789838,174.66355610583875</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>-38.36701337114269,174.66442093898408</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-38.38454268919923,174.65502199021904</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-38.383968651664986,174.65557495412668</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-38.38337165445016,174.65606585973464</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-38.38274717645086,174.65648248363152</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-38.3821223862452,174.6568982783761</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-38.38149107622565,174.65729646124586</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-38.380871486053955,174.65772634451827</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-38.38017207333094,174.6579404377073</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-38.37950294530373,174.65824375657306</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-38.378846816038234,174.65858034579443</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-38.378136479102395,174.65868975890967</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-38.37745900784237,174.65893481146222</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-38.37677013076561,174.65912936362687</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-38.37611169587761,174.65945880409998</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-38.3754443137779,174.65974863568533</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-38.37473953775252,174.659885786409</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-38.374053863464724,174.6601244263357</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>-38.37340474564573,174.66048603353292</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>-38.37274618204895,174.66080423159408</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>-38.372103076195174,174.66117508173318</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>-38.37145300043015,174.6615200521074</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>-38.37076926899006,174.66174716987942</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>-38.370109258359896,174.66206067494923</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>-38.36948855430309,174.6625135999569</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>-38.368857271256374,174.66292902831324</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>-38.3682229552616,174.6633401568617</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>-38.36754110158753,174.66357821638977</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>-38.36704912709519,174.6645629722445</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-38.38454793903276,174.65503618352753</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-38.3839714489955,174.65558251693864</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-38.38337311058335,174.65606979651466</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-38.3827501270183,174.65649046073233</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-38.382124148911124,174.65690304388158</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-38.38149222578384,174.65729956916067</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-38.38087045145818,174.6577235474153</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-38.38017203501263,174.65794033411188</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-38.37950147080136,174.65823920511443</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-38.37884153380592,174.6585594189251</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-38.37813533665205,174.6586846977536</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-38.37745689680354,174.65892545941014</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-38.37676913733886,174.65912496270198</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-38.37611219258677,174.65946100454386</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-38.37544187991929,174.65973785360484</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-38.374736602127996,174.6598737614207</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>-38.37405047359467,174.66011223106446</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>-38.373401033511406,174.66047337815942</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>-38.37274794372968,174.66081023748401</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>-38.37210445976769,174.66117980089066</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>-38.37145368037818,174.66152241721053</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>-38.37077148680908,174.66175503527575</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>-38.370114058543024,174.6620776985404</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>-38.36949162274425,174.66252448204503</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>-38.368855326914236,174.66292213278615</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>-38.36825330433498,174.66345300461256</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>-38.36754110158753,174.66357821638977</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>-38.36704912709519,174.6645629722445</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD329"/>
+  <dimension ref="A1:AD330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31983,7 +31983,7 @@
         <v>353.58</v>
       </c>
       <c r="AA329" t="n">
-        <v>333.52</v>
+        <v>343.94</v>
       </c>
       <c r="AB329" t="n">
         <v>348.64</v>
@@ -31994,6 +31994,102 @@
       <c r="AD329" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="C330" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="D330" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="E330" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="F330" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G330" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="H330" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="I330" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="J330" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="K330" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="L330" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="M330" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="N330" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="O330" t="n">
+        <v>366.15</v>
+      </c>
+      <c r="P330" t="n">
+        <v>360.28</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="R330" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="S330" t="n">
+        <v>374.68</v>
+      </c>
+      <c r="T330" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="U330" t="n">
+        <v>370.98</v>
+      </c>
+      <c r="V330" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="W330" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="X330" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>284.37</v>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32008,7 +32104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35341,6 +35437,16 @@
       </c>
       <c r="B333" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -35509,28 +35615,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6307458219607904</v>
+        <v>-0.6255866509965672</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3626679963268912</v>
+        <v>0.3587492792755761</v>
       </c>
       <c r="M2" t="n">
-        <v>5.010239047143869</v>
+        <v>5.027046680286984</v>
       </c>
       <c r="N2" t="n">
-        <v>37.67362015486183</v>
+        <v>37.80251368877632</v>
       </c>
       <c r="O2" t="n">
-        <v>6.137884012822483</v>
+        <v>6.148374881932324</v>
       </c>
       <c r="P2" t="n">
-        <v>366.8515576735019</v>
+        <v>366.7942295841382</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35587,28 +35693,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5235960263100882</v>
+        <v>-0.5201182165341269</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3238672630585502</v>
+        <v>0.3214572119568895</v>
       </c>
       <c r="M3" t="n">
-        <v>4.453064488584364</v>
+        <v>4.458682964866092</v>
       </c>
       <c r="N3" t="n">
-        <v>30.84108812838864</v>
+        <v>30.85795198488318</v>
       </c>
       <c r="O3" t="n">
-        <v>5.553475319868509</v>
+        <v>5.554993427978396</v>
       </c>
       <c r="P3" t="n">
-        <v>350.7205226777692</v>
+        <v>350.6818776723974</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35665,28 +35771,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3356709853388611</v>
+        <v>-0.3338488074176666</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2761421942968122</v>
+        <v>0.2747638527931513</v>
       </c>
       <c r="M4" t="n">
-        <v>3.130578544159193</v>
+        <v>3.132360920576142</v>
       </c>
       <c r="N4" t="n">
-        <v>15.91549654990531</v>
+        <v>15.89748439015317</v>
       </c>
       <c r="O4" t="n">
-        <v>3.989423084846393</v>
+        <v>3.987164956476365</v>
       </c>
       <c r="P4" t="n">
-        <v>339.387076085483</v>
+        <v>339.3668282628333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35743,28 +35849,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06257532051532178</v>
+        <v>-0.05945220615929527</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01022668694711726</v>
+        <v>0.009254467886704032</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35622459046748</v>
+        <v>3.364030836770409</v>
       </c>
       <c r="N5" t="n">
-        <v>20.42109563397955</v>
+        <v>20.44822071837136</v>
       </c>
       <c r="O5" t="n">
-        <v>4.518970638760507</v>
+        <v>4.521970888713389</v>
       </c>
       <c r="P5" t="n">
-        <v>326.4208650468717</v>
+        <v>326.3861613744915</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35821,28 +35927,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0973550663921483</v>
+        <v>-0.09219453416544296</v>
       </c>
       <c r="J6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01402913943958339</v>
+        <v>0.0125884341988115</v>
       </c>
       <c r="M6" t="n">
-        <v>4.823703304348346</v>
+        <v>4.834870018817321</v>
       </c>
       <c r="N6" t="n">
-        <v>35.8940330412868</v>
+        <v>36.028464116728</v>
       </c>
       <c r="O6" t="n">
-        <v>5.991162912263929</v>
+        <v>6.002371541043424</v>
       </c>
       <c r="P6" t="n">
-        <v>321.402972691408</v>
+        <v>321.3456294758587</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35899,28 +36005,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3394137018413315</v>
+        <v>-0.3316806247768815</v>
       </c>
       <c r="J7" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0921103294795802</v>
+        <v>0.08808352105467043</v>
       </c>
       <c r="M7" t="n">
-        <v>6.463884219446611</v>
+        <v>6.486801891508759</v>
       </c>
       <c r="N7" t="n">
-        <v>61.18649496442377</v>
+        <v>61.54737102310863</v>
       </c>
       <c r="O7" t="n">
-        <v>7.822179681164565</v>
+        <v>7.845213255425797</v>
       </c>
       <c r="P7" t="n">
-        <v>323.7847077469918</v>
+        <v>323.6987787215569</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35977,28 +36083,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4636610152670244</v>
+        <v>-0.4584976082378769</v>
       </c>
       <c r="J8" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K8" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1327473899444275</v>
+        <v>0.1304922285528526</v>
       </c>
       <c r="M8" t="n">
-        <v>6.982526296979177</v>
+        <v>6.988972107305235</v>
       </c>
       <c r="N8" t="n">
-        <v>75.68204942083646</v>
+        <v>75.69581568235412</v>
       </c>
       <c r="O8" t="n">
-        <v>8.699543058163254</v>
+        <v>8.700334228198026</v>
       </c>
       <c r="P8" t="n">
-        <v>329.060731422783</v>
+        <v>329.0033562627737</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36055,28 +36161,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4673214402943882</v>
+        <v>-0.4560308283653921</v>
       </c>
       <c r="J9" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1093067047728236</v>
+        <v>0.1040472158109627</v>
       </c>
       <c r="M9" t="n">
-        <v>7.692992135312491</v>
+        <v>7.728586662446451</v>
       </c>
       <c r="N9" t="n">
-        <v>95.79439224035974</v>
+        <v>96.66886445545573</v>
       </c>
       <c r="O9" t="n">
-        <v>9.7874609700555</v>
+        <v>9.832032569893965</v>
       </c>
       <c r="P9" t="n">
-        <v>335.7284407551868</v>
+        <v>335.6025455924249</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36133,28 +36239,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4752548226377855</v>
+        <v>-0.4657065127996267</v>
       </c>
       <c r="J10" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K10" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1236115213423041</v>
+        <v>0.118884589355565</v>
       </c>
       <c r="M10" t="n">
-        <v>7.486075041796251</v>
+        <v>7.517926599742429</v>
       </c>
       <c r="N10" t="n">
-        <v>86.04614024204901</v>
+        <v>86.61574822596253</v>
       </c>
       <c r="O10" t="n">
-        <v>9.276105877039621</v>
+        <v>9.306758201756535</v>
       </c>
       <c r="P10" t="n">
-        <v>347.29871447059</v>
+        <v>347.1922215028545</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36211,28 +36317,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4212469035986709</v>
+        <v>-0.4156217810464681</v>
       </c>
       <c r="J11" t="n">
+        <v>329</v>
+      </c>
+      <c r="K11" t="n">
         <v>328</v>
       </c>
-      <c r="K11" t="n">
-        <v>327</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07565889736167242</v>
+        <v>0.07403478938554664</v>
       </c>
       <c r="M11" t="n">
-        <v>8.678484770137009</v>
+        <v>8.680982636680914</v>
       </c>
       <c r="N11" t="n">
-        <v>115.9279701673294</v>
+        <v>115.8609594245575</v>
       </c>
       <c r="O11" t="n">
-        <v>10.76698519397744</v>
+        <v>10.76387288221844</v>
       </c>
       <c r="P11" t="n">
-        <v>353.9239623586253</v>
+        <v>353.8611155563187</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36289,28 +36395,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3651528759692116</v>
+        <v>-0.3570643453084841</v>
       </c>
       <c r="J12" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K12" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05343911536635992</v>
+        <v>0.05127552823223624</v>
       </c>
       <c r="M12" t="n">
-        <v>8.985023237077504</v>
+        <v>9.004269613100234</v>
       </c>
       <c r="N12" t="n">
-        <v>127.2655445886541</v>
+        <v>127.4770004732142</v>
       </c>
       <c r="O12" t="n">
-        <v>11.28120315341649</v>
+        <v>11.29057130853945</v>
       </c>
       <c r="P12" t="n">
-        <v>359.1581493960603</v>
+        <v>359.0682706128691</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36367,28 +36473,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5079889435433974</v>
+        <v>-0.5000781323846805</v>
       </c>
       <c r="J13" t="n">
+        <v>329</v>
+      </c>
+      <c r="K13" t="n">
         <v>328</v>
       </c>
-      <c r="K13" t="n">
-        <v>327</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.08365482082288156</v>
+        <v>0.08144078295192514</v>
       </c>
       <c r="M13" t="n">
-        <v>9.74403439902636</v>
+        <v>9.755614267368768</v>
       </c>
       <c r="N13" t="n">
-        <v>151.153837252889</v>
+        <v>151.2594944302396</v>
       </c>
       <c r="O13" t="n">
-        <v>12.29446368301151</v>
+        <v>12.2987598736718</v>
       </c>
       <c r="P13" t="n">
-        <v>365.3372692848679</v>
+        <v>365.2488855776043</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36445,28 +36551,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4558953923462876</v>
+        <v>-0.4477422863194723</v>
       </c>
       <c r="J14" t="n">
+        <v>329</v>
+      </c>
+      <c r="K14" t="n">
         <v>328</v>
       </c>
-      <c r="K14" t="n">
-        <v>327</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.064710620784177</v>
+        <v>0.06268687277720408</v>
       </c>
       <c r="M14" t="n">
-        <v>9.860655852251144</v>
+        <v>9.871223952601847</v>
       </c>
       <c r="N14" t="n">
-        <v>160.6361820116757</v>
+        <v>160.7481624253575</v>
       </c>
       <c r="O14" t="n">
-        <v>12.67423299500509</v>
+        <v>12.67864986602901</v>
       </c>
       <c r="P14" t="n">
-        <v>369.2326963583583</v>
+        <v>369.1416056064865</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36523,28 +36629,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9191756723424944</v>
+        <v>-0.9134616479699189</v>
       </c>
       <c r="J15" t="n">
+        <v>329</v>
+      </c>
+      <c r="K15" t="n">
         <v>328</v>
       </c>
-      <c r="K15" t="n">
-        <v>327</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2244289792102171</v>
+        <v>0.2229595109178605</v>
       </c>
       <c r="M15" t="n">
-        <v>9.499839632759533</v>
+        <v>9.494229165431872</v>
       </c>
       <c r="N15" t="n">
-        <v>156.1285092609833</v>
+        <v>155.9480611079917</v>
       </c>
       <c r="O15" t="n">
-        <v>12.49513942543193</v>
+        <v>12.4879166039813</v>
       </c>
       <c r="P15" t="n">
-        <v>380.7234223841172</v>
+        <v>380.6595823243166</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36601,28 +36707,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6340578597479674</v>
+        <v>-0.6329088701991766</v>
       </c>
       <c r="J16" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K16" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1354282671838974</v>
+        <v>0.1356900572771828</v>
       </c>
       <c r="M16" t="n">
-        <v>8.903203625349759</v>
+        <v>8.881977800036134</v>
       </c>
       <c r="N16" t="n">
-        <v>135.2470489155959</v>
+        <v>134.845143812601</v>
       </c>
       <c r="O16" t="n">
-        <v>11.62957647189251</v>
+        <v>11.61228417722375</v>
       </c>
       <c r="P16" t="n">
-        <v>375.1858010026948</v>
+        <v>375.172845651242</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36679,28 +36785,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8002131296937743</v>
+        <v>-0.7891367335938511</v>
       </c>
       <c r="J17" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K17" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1221935801946132</v>
+        <v>0.1193916249745626</v>
       </c>
       <c r="M17" t="n">
-        <v>12.09082413368565</v>
+        <v>12.09831520375168</v>
       </c>
       <c r="N17" t="n">
-        <v>244.4865969485718</v>
+        <v>244.8271447493127</v>
       </c>
       <c r="O17" t="n">
-        <v>15.6360671829131</v>
+        <v>15.64695320978857</v>
       </c>
       <c r="P17" t="n">
-        <v>377.4326867617013</v>
+        <v>377.3084383827386</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36757,28 +36863,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3939675720757848</v>
+        <v>-0.387380543059362</v>
       </c>
       <c r="J18" t="n">
+        <v>329</v>
+      </c>
+      <c r="K18" t="n">
         <v>328</v>
       </c>
-      <c r="K18" t="n">
-        <v>327</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.04757114500754345</v>
+        <v>0.04622171140830977</v>
       </c>
       <c r="M18" t="n">
-        <v>10.16297515362089</v>
+        <v>10.16151355166319</v>
       </c>
       <c r="N18" t="n">
-        <v>166.4761012641894</v>
+        <v>166.3624716921824</v>
       </c>
       <c r="O18" t="n">
-        <v>12.90256181012862</v>
+        <v>12.89815768597137</v>
       </c>
       <c r="P18" t="n">
-        <v>375.6696969931199</v>
+        <v>375.5961789128432</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36835,28 +36941,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1998530557861724</v>
+        <v>-0.1934505573937042</v>
       </c>
       <c r="J19" t="n">
+        <v>329</v>
+      </c>
+      <c r="K19" t="n">
         <v>328</v>
       </c>
-      <c r="K19" t="n">
-        <v>327</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01258346396438947</v>
+        <v>0.01184270185277225</v>
       </c>
       <c r="M19" t="n">
-        <v>10.63360774482824</v>
+        <v>10.63300730652635</v>
       </c>
       <c r="N19" t="n">
-        <v>167.2459236554337</v>
+        <v>167.1058282346795</v>
       </c>
       <c r="O19" t="n">
-        <v>12.9323595548312</v>
+        <v>12.92694195216639</v>
       </c>
       <c r="P19" t="n">
-        <v>368.9343426338896</v>
+        <v>368.8627282818454</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36913,28 +37019,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01427220193580357</v>
+        <v>0.02305211651668345</v>
       </c>
       <c r="J20" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K20" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L20" t="n">
-        <v>5.58713272001965e-05</v>
+        <v>0.0001460790491976116</v>
       </c>
       <c r="M20" t="n">
-        <v>11.17421427946538</v>
+        <v>11.18389474609386</v>
       </c>
       <c r="N20" t="n">
-        <v>196.4449215487563</v>
+        <v>196.5527556699895</v>
       </c>
       <c r="O20" t="n">
-        <v>14.0158810478955</v>
+        <v>14.01972737502372</v>
       </c>
       <c r="P20" t="n">
-        <v>360.455218264668</v>
+        <v>360.357656906227</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36991,28 +37097,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06841443613666409</v>
+        <v>0.07472294018835186</v>
       </c>
       <c r="J21" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K21" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00149979816626189</v>
+        <v>0.001795289780501474</v>
       </c>
       <c r="M21" t="n">
-        <v>10.12443599172041</v>
+        <v>10.11859367344903</v>
       </c>
       <c r="N21" t="n">
-        <v>166.0742840962383</v>
+        <v>165.9229994312623</v>
       </c>
       <c r="O21" t="n">
-        <v>12.8869811863073</v>
+        <v>12.88111017852352</v>
       </c>
       <c r="P21" t="n">
-        <v>358.2950427354998</v>
+        <v>358.2242271933427</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37069,28 +37175,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2119965223567154</v>
+        <v>0.2177610563704962</v>
       </c>
       <c r="J22" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K22" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0130861870707587</v>
+        <v>0.01385524545765016</v>
       </c>
       <c r="M22" t="n">
-        <v>10.69452385070532</v>
+        <v>10.68515071456532</v>
       </c>
       <c r="N22" t="n">
-        <v>180.6404984441727</v>
+        <v>180.385034497199</v>
       </c>
       <c r="O22" t="n">
-        <v>13.44025663609787</v>
+        <v>13.43074958806094</v>
       </c>
       <c r="P22" t="n">
-        <v>353.1427930817131</v>
+        <v>353.07808382606</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37147,28 +37253,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1879997594029888</v>
+        <v>0.2025653531825644</v>
       </c>
       <c r="J23" t="n">
+        <v>329</v>
+      </c>
+      <c r="K23" t="n">
         <v>328</v>
       </c>
-      <c r="K23" t="n">
-        <v>327</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.009073791443297785</v>
+        <v>0.01048396406229857</v>
       </c>
       <c r="M23" t="n">
-        <v>11.650035805482</v>
+        <v>11.68791635525706</v>
       </c>
       <c r="N23" t="n">
-        <v>205.9685340251564</v>
+        <v>207.2545071943049</v>
       </c>
       <c r="O23" t="n">
-        <v>14.35160388336985</v>
+        <v>14.39633658936554</v>
       </c>
       <c r="P23" t="n">
-        <v>346.8550736701577</v>
+        <v>346.6921520266487</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37225,28 +37331,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1573257218285524</v>
+        <v>0.1717998665758167</v>
       </c>
       <c r="J24" t="n">
+        <v>329</v>
+      </c>
+      <c r="K24" t="n">
         <v>328</v>
       </c>
-      <c r="K24" t="n">
-        <v>327</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.008026102914195143</v>
+        <v>0.009502940779832714</v>
       </c>
       <c r="M24" t="n">
-        <v>9.960506252816435</v>
+        <v>10.00612857700859</v>
       </c>
       <c r="N24" t="n">
-        <v>163.2408152683304</v>
+        <v>164.6330984235932</v>
       </c>
       <c r="O24" t="n">
-        <v>12.77657290780006</v>
+        <v>12.83094300601453</v>
       </c>
       <c r="P24" t="n">
-        <v>345.9933831961844</v>
+        <v>345.8314844444893</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37303,28 +37409,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07232859480265688</v>
+        <v>0.08147162295173402</v>
       </c>
       <c r="J25" t="n">
+        <v>329</v>
+      </c>
+      <c r="K25" t="n">
         <v>328</v>
       </c>
-      <c r="K25" t="n">
-        <v>327</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.001602074107611817</v>
+        <v>0.002035032290671368</v>
       </c>
       <c r="M25" t="n">
-        <v>10.56403901251327</v>
+        <v>10.58399421157463</v>
       </c>
       <c r="N25" t="n">
-        <v>173.9702121346163</v>
+        <v>174.1939497558005</v>
       </c>
       <c r="O25" t="n">
-        <v>13.18977680382107</v>
+        <v>13.1982555573</v>
       </c>
       <c r="P25" t="n">
-        <v>341.7158458670073</v>
+        <v>341.6135776591169</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37381,28 +37487,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2606830927493058</v>
+        <v>0.264420348558946</v>
       </c>
       <c r="J26" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K26" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01723214273574414</v>
+        <v>0.01781308032126916</v>
       </c>
       <c r="M26" t="n">
-        <v>11.53161942507553</v>
+        <v>11.51532492083225</v>
       </c>
       <c r="N26" t="n">
-        <v>208.8379809482023</v>
+        <v>208.330938830748</v>
       </c>
       <c r="O26" t="n">
-        <v>14.45122766231998</v>
+        <v>14.43367378149956</v>
       </c>
       <c r="P26" t="n">
-        <v>338.3563263254336</v>
+        <v>338.3147983868334</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37459,28 +37565,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.08501567873472152</v>
+        <v>-0.07647166467560917</v>
       </c>
       <c r="J27" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K27" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L27" t="n">
-        <v>0.00134491346146226</v>
+        <v>0.001094238411488813</v>
       </c>
       <c r="M27" t="n">
-        <v>11.89056426536364</v>
+        <v>11.87391466905788</v>
       </c>
       <c r="N27" t="n">
-        <v>289.1953637259375</v>
+        <v>288.4845472290928</v>
       </c>
       <c r="O27" t="n">
-        <v>17.00574502119614</v>
+        <v>16.98483285843852</v>
       </c>
       <c r="P27" t="n">
-        <v>339.2095401138375</v>
+        <v>339.1146680500513</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -37537,28 +37643,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1870230754629651</v>
+        <v>-0.1839648083727611</v>
       </c>
       <c r="J28" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K28" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L28" t="n">
-        <v>0.013827581442031</v>
+        <v>0.01345461682623428</v>
       </c>
       <c r="M28" t="n">
-        <v>9.265016762570019</v>
+        <v>9.253932511391383</v>
       </c>
       <c r="N28" t="n">
-        <v>134.4216157084351</v>
+        <v>134.0985690674634</v>
       </c>
       <c r="O28" t="n">
-        <v>11.59403362546595</v>
+        <v>11.58009365538394</v>
       </c>
       <c r="P28" t="n">
-        <v>348.28864046671</v>
+        <v>348.2546573693749</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -37615,28 +37721,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01213778886745289</v>
+        <v>-0.0248679821655955</v>
       </c>
       <c r="J29" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K29" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L29" t="n">
-        <v>2.419347622495405e-05</v>
+        <v>9.854964392008725e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>10.87971967539132</v>
+        <v>11.07681941920645</v>
       </c>
       <c r="N29" t="n">
-        <v>323.4717552683244</v>
+        <v>334.3143706502516</v>
       </c>
       <c r="O29" t="n">
-        <v>17.9853205495016</v>
+        <v>18.28426565794349</v>
       </c>
       <c r="P29" t="n">
-        <v>345.9187263018569</v>
+        <v>346.3328079009406</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -37674,7 +37780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD329"/>
+  <dimension ref="A1:AD330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87518,7 +87624,7 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>-38.36825330433498,174.66345300461256</t>
+          <t>-38.3682229552616,174.6633401568617</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr">
@@ -87534,6 +87640,158 @@
       <c r="AD329" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-38.384543378958476,174.6550238550332</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-38.38397194715021,174.65558386374087</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-38.38337372369204,174.6560714541063</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-38.38275330749944,174.65649905942612</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-38.38212893876317,174.65691599362577</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-38.38149372020936,174.65730360945008</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-38.380869761727645,174.65772168268003</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-38.38017034900692,174.65793577591288</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-38.37950280814072,174.65824333318153</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-38.37883735203596,174.6585428518223</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-38.37813424387325,174.65867985664798</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-38.3774548105997,174.6589162173827</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-38.37676613222193,174.6591116499048</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-38.37610417072913,174.6594254673793</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-38.37544421443674,174.6597481956004</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-38.37472950324894,174.6598446828165</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>-38.374054013458945,174.6601249659495</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>-38.373400247042085,174.6604706969364</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>-38.372738820736856,174.66077913555714</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>-38.372098170800136,174.6611583501761</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>-38.37144901346116,174.66150618400363</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>-38.37076431687167,174.66172960742074</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>-38.370109835597226,174.66206272208981</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>-38.36949760772056,174.6625457075066</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>-38.36886070423446,174.66294120322914</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>-38.36823026584507,174.66336733994885</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>-38.36754110158753,174.66357821638977</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>-38.36704912709519,174.6645629722445</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
